--- a/output/(山本)規範適合性_文法適合性_再構成.xlsx
+++ b/output/(山本)規範適合性_文法適合性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,14 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>日本語の構文規則に基づき、主格、目的格、述語などの構成要素が欠落なく配置されている。特に並列する動作において、接続を助ける語（動詞の連用形や助詞）が不足していないかを判定の指標とする。</t>
+          <t>主語、述語、修飾語の構成要素を過不足なく配置し、JTF日本語標準スタイルガイドに準拠して、構文として完結した一文を形成している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】本システムは、ログイン画面においてIDを入力、送信ボタンを押下する。（接続を補助する動詞や助詞が欠落している）。
-→【適合例】本システムは、ログイン画面においてIDを入力し、送信ボタンを押下する構成とする。</t>
+【非適合例】システムが異常終了した場合のエラーログ出力処理。（述語が存在せず、文として完結していない。）
+→【適合例】システムが異常終了した場合、エラーログを出力する。</t>
         </is>
       </c>
     </row>
@@ -480,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>文や節が持つ論理的なつながりを分析し、順接、逆接、並列、選択等の意図に応じた適切な接続詞を選択している。文脈上の因果関係が設計の論理と一致していることを確認の拠点とする。</t>
+          <t>前後の文や節が持つ論理関係を特定し、条件分岐の処理フローや仕様上の因果関係と矛盾しない接続詞を選択している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】サーバーの負荷が高まるとレスポンスが低下する。しかし、サーバー資源の増強が必要である。（論理的に順接の関係だが、逆接の接続詞を使用している）。
-→【適合例】サーバーの負荷が高まるとレスポンスが低下する。したがって、サーバー資源の増強が必要である。</t>
+【非適合例】パスワードの有効期限が切れている。しかし、ログイン画面に警告メッセージを表示する。（順接の文脈に逆接の接続詞を使用しており、仕様の因果関係が破綻している。）
+→【適合例】パスワードの有効期限が切れている。そのため、ログイン画面に警告メッセージを表示する。</t>
         </is>
       </c>
     </row>
@@ -499,14 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>格助詞や副助詞を適切に使い分け、単語間の関係や動作の主体・対象・方向を厳密に定義している。特にデータの移動や処理の帰属が、助詞の選択によって一義的に定まっているかを検証する。</t>
+          <t>システムの振る舞いにおける主体、対象、方向などの関係性を一意に特定するため、動詞が要求する文法的な連携規則に従って格助詞を配置している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】ユーザーは入力フォームをデータを送信する。（格助詞「を」が連続しており、目的語の関係性が不明瞭になっている）。
-→【適合例】ユーザーが入力フォームのデータを送信する。</t>
+【非適合例】管理者権限を持つユーザーが、新規アカウントを登録を承認する。（格助詞「を」が連続しており、動詞との連携が破綻している。）
+→【適合例】管理者権限を持つユーザーが、新規アカウントの登録を承認する。</t>
         </is>
       </c>
     </row>
@@ -518,14 +518,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>文頭で提示した主語と、文末の述語が、意味的および文法的に矛盾なく対応している。機能の目的や概要を述べる文において、記述の主体と結末が論理的に整合しているかを尺度とする。</t>
+          <t>文頭の主語が示すアクタや事象の性質と、文末の述語が示す動作や状態について、仕様上の整合性を保ちながら文法的に一致する構造で記述している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】本機能の目的は、ユーザーが過去の注文履歴を閲覧することを可能にします。（主語「目的は」に対して、述語が「可能にします」となっており対応していない）。
-→【適合例】本機能の目的は、ユーザーが過去の注文履歴を閲覧できるようにすることである。</t>
+【非適合例】本バッチ処理の目的は、毎日深夜に売上データを集計し、集計結果をデータベースに保存する。（主語「目的は」に対して、述語「保存する」がねじれており、仕様の意図が曖昧になっている。）
+→【適合例】本バッチ処理の目的は、毎日深夜に売上データを集計し、集計結果をデータベースに保存することである。</t>
         </is>
       </c>
     </row>
@@ -537,14 +537,33 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>修飾語が本来修飾すべき対象と一義的に結びつくよう、語順の最適化や読点の配置を行っている。複数の解釈が生じる余地を排除し、実装者が仕様を誤認しない構造であることを確認する。</t>
+          <t>提示した処理条件や修飾語句に対して、呼応する係り先となる被修飾語句を明記し、プログラム実装時に生じる意味の不整合を排除している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】新しく開発した機能のテスト仕様書を作成する。（副詞「新しく」が「開発した」にかかるのか「作成する」にかかるのかが曖昧である）。
-→【適合例】新しく開発した機能について、そのテスト仕様書を作成する。</t>
+【非適合例】外部APIからのレスポンスコードが500系エラーであった場合は。（条件に対する係り先の述語が存在せず、例外処理の動作が定義されていない。）
+→【適合例】外部APIからのレスポンスコードが500系エラーであった場合は、システム管理者にアラートメールを送信する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>係り受けが正しい（違反の例：係り先が存在しない）</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>修飾語句が複数の名詞に隣接する場合、読点の配置や語順の変更によって係り受けの適用範囲を限定し、データ処理のスコープを一意に特定している。</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>★新規追加
+【非適合例】削除されたユーザーの投稿と画像データ。（「削除された」が投稿のみにかかるか、画像データにもかかるか曖昧であり、処理対象を誤認するリスクがある。）
+→【適合例】ユーザーの投稿、および削除された画像データ。</t>
         </is>
       </c>
     </row>
